--- a/docs/package/05_Delivery/Upload_Templates/Talkbot_Call_Results_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Talkbot_Call_Results_Template.xlsx
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Renewals &gt; Talkbot Calls &gt; Upload results</t>
+    <t xml:space="preserve">Policy Servicing &gt; Renewals &gt; Talkbot Calls &gt; Upload results</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
